--- a/data/daily/2026-10/2026-10-06.xlsx
+++ b/data/daily/2026-10/2026-10-06.xlsx
@@ -1195,14 +1195,39 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1242,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,17 +1267,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,17 +1292,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1292,17 +1317,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="323850" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1317,17 +1342,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1342,35 +1367,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="342900" cy="457200"/>
+    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -1450,27 +1450,52 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1478,24 +1503,24 @@
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1503,74 +1528,74 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
+    <ext cx="866775" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1578,54 +1603,29 @@
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -2598,21 +2598,9 @@
       <c r="J2" t="n">
         <v>16226</v>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>뛰어난 피로 해소 — 피로 회복 및 에너지를 충전하는 데 큰 도움이 됨</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>선물용으로 추천 — 포장과 구성이 고급스러워 감사한 마음을 전하는 선물용으로 매우 적합함</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>편리한 액상 타입 — 액상과 알약 형태가 함께 들어있어 섭취가 편리하고 맛도 우수함</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -2655,23 +2643,11 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15539</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>우수한 피로 회복 — 피곤할 때 섭취 시 아침이 개운해지고 활력을 되찾는 데 효과적임</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>간편한 휴대와 섭취 — 물이 필요 없는 샷 제형으로 가방에 휴대하며 하나씩 꺼내 먹기 편리함</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>거부감 없는 맛 — 망고맛 등 쥬스처럼 상큼하고 맛있어서 맛에 대한 거부감이 전혀 없음</t>
-        </is>
-      </c>
+        <v>15540</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -2714,24 +2690,12 @@
         <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>3395</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>빠른 피로 회복 — 힘들거나 피곤할 때 섭취하면 다음 날 몸이 가뿐해지는 것을 체감함</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>고품격 패키지 디자인 — 포장 상태가 고급스러워 선물을 고를 때나 받을 때 만족도가 매우 높음</t>
-        </is>
-      </c>
+        <v>3396</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>발송인 확인 불가 — 카카오톡 선물 수령 시 보낸 사람의 정보를 알기 어렵고 고객센터 문의도 미흡함</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
@@ -2775,21 +2739,9 @@
       <c r="J5" t="n">
         <v>6507</v>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>편리한 구미 제형 — 알약을 삼키기 힘들거나 수술 후 목넘김이 어려운 사람도 편하게 씹어 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>우수한 맛과 식감 — 탱글하고 쫄깃한 식감에 맛이 좋아 간식처럼 매일 챙겨 먹기 적합함</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>귀여운 패키지 — 감귤 모양의 손잡이가 달린 케이스와 귀여운 키캡 증정 구성으로 소장 가치가 높음</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -2805,51 +2757,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
+          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>뉴트리포유</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19,900원</t>
+          <t>52,900원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10056171</t>
+          <t>https://gift.kakao.com/product/10903147</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260219100848_1c2cc8073bd44eaab9f09d6b8fb8f34c.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260928130637_4b5e189e4cc74b40bc33bd3c75d10253.jpg</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>8741</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>아침 활력 증진 — 피곤할 때 먹으면 기력 회복에 좋고 아침에 일어날 때 몸이 다르게 느껴짐</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>알찬 에디션 구성 — 7입에 2입을 추가로 증정하여 가성비가 훌륭하고 단독 에디션 패키지가 깔끔함</t>
-        </is>
-      </c>
+        <v>812</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>다소 아쉬운 부피 — 소포장 제품이라 선물로 건넸을 때 외관상 풍성해 보이지는 않음</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
@@ -2864,50 +2804,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병</t>
+          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>뉴트리포유</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>52,900원</t>
+          <t>19,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10903147</t>
+          <t>https://gift.kakao.com/product/10056171</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260928130637_4b5e189e4cc74b40bc33bd3c75d10253.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260219100848_1c2cc8073bd44eaab9f09d6b8fb8f34c.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>811</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>휴대성과 편리함 — 가볍게 들고 다니며 물 없이 마시기 좋고 섭취 방법이 무척 간편함</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>우수한 가성비 — 부담스러운 가격대의 타 브랜드 대비 합리적인 가격으로 구매하기 좋음</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>신속한 배송 — 배송이 빠르고 안전하게 도착하여 기다림 없이 바로 섭취할 수 있음</t>
-        </is>
-      </c>
+        <v>8741</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -2952,16 +2880,8 @@
       <c r="J8" t="n">
         <v>811</v>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>선물에 최적화된 패키지 — 종이가방과 고급스러운 전용 박스 포장 덕분에 명절이나 감사의 선물로 제격임</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>면역력 및 활력 개선 — 환절기 감기 예방과 지친 일상 속 빠른 면역력 관리에 매우 우수함</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -2970,7 +2890,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2978,50 +2898,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
+          <t>'성별 맞춤 설계' 오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 - 시그니처 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>정관장</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>39,000원</t>
+          <t>59,800원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12159594</t>
+          <t>https://gift.kakao.com/product/8167919</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260812135521_25667cc1efc34a698d1813fe75189344.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260928090417_28fb45c20b10424fb6c1bd6211e4e4e9.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>1737</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>독특한 밀폐 용기 — 버튼을 눌러 섞어 마시는 신선한 방식으로 재미를 주며 변질 우려가 없음</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>출산 및 육아 체력 관리 — 체력 소모가 극심한 출산 후 육아맘에게 활기를 북돋아 주는 센스 있는 선물임</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>고급스러운 무게감 — 용기와 패키지에서 묵직한 고급스러움이 느껴지며 가격 부담도 적어 만족함</t>
-        </is>
-      </c>
+        <v>780</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -3029,7 +2937,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -3037,50 +2945,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>'성별 맞춤 설계' 오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 - 시그니처 기프트 에디션 (공식수입)</t>
+          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>정관장</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>59,800원</t>
+          <t>39,000원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/8167919</t>
+          <t>https://gift.kakao.com/product/12159594</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260928090417_28fb45c20b10424fb6c1bd6211e4e4e9.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260812135521_25667cc1efc34a698d1813fe75189344.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>780</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>성별 맞춤 영양 설계 — 남성과 여성의 건강에 맞추어 선택이 가능하고 영양소 함량도 이뮨보다 풍부함</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>쓴맛 없는 부드러움 — 비타민 특유의 쓰고 텁텁한 맛이 없어서 부담 없이 마시기에 용이함</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>편리한 일상 휴대 — 가방에 가볍게 넣고 다닐 수 있는 콤팩트한 크기로 섭취가 간편함</t>
-        </is>
-      </c>
+        <v>1740</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -3125,27 +3021,11 @@
       <c r="J11" t="n">
         <v>948</v>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>믿을 수 있는 영국산 원료 — 고품질의 영국산 비타민C 원료를 사용하여 안전하고 신뢰를 줌</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>우수한 컨디션 개선 — 복용 후 활력이 생기고 피부 건강과 아침 기상 시 가뿐함을 확실히 체감함</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>자극적이고 신 맛 — 함량이 높아 신맛이 매우 자극적이고 맛이 없게 느껴질 수 있음</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>복용이 불편한 제형 — 가루 형태라 입에 털어먹을 때 불편하므로 캡슐 형태로 개선되기를 희망함</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
     <row r="12" ht="38" customHeight="1">
@@ -3186,23 +3066,11 @@
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>180</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>맛있는 이색 효소 — 효소 특유의 불쾌한 맛없이 크림소다, 유자 등 새롭고 달달한 맛을 구현함</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>효과적인 소화 도움 — 식사 후 가볍게 털어먹으면 속 더부룩함이 가라앉고 소화가 편해짐</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>콜라보 굿즈 만족도 — 예쁜 리센느 포토카드와 엽서가 함께 포함되어 소장 가치를 더해줌</t>
-        </is>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
@@ -3247,22 +3115,10 @@
       <c r="J13" t="n">
         <v>60</v>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>잡내 없는 촉촉함 — 닭가슴살 특유의 비린내가 전혀 나지 않고 부드러운 식감이 우수함</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>다채로운 맛과 구성 — 다양한 종류와 양념으로 구성되어 질리지 않고 맛있게 식단을 관리할 수 있음</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>특정 라인업의 부재 — 가장 인기가 높은 그릴 형태의 파우치 제품이 구성에 빠져 있어 다소 아쉬움</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
     </row>
@@ -3306,21 +3162,9 @@
       <c r="J14" t="n">
         <v>1689</v>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>속이 편해지는 소화 — 밀가루나 과식을 한 뒤에 섭취하면 속 편안함과 뛰어난 소화력을 선사함</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>구수한 고구마 맛 — 자극적이거나 텁텁하지 않고 구수한 고구마 맛이 나서 전 세대가 좋아함</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>알찬 무료 증정품 — 곡물바, 차, 파로효소 등 맛있는 사은품이 넉넉하게 추가되어 혜택이 좋음</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
@@ -3365,22 +3209,10 @@
       <c r="J15" t="n">
         <v>754</v>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>감동적인 전용 포장 — 오간자 에디션과 예쁜 전용 가방이 함께 구성되어 패키지를 열 때 기분이 무척 좋음</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>비린 맛 없는 청량함 — 콜라겐 특유의 비린 맛 없이 상큼하고 깔끔하여 매일 먹기에 편안함</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>다소 높은 가격대 — 일반 영양제 대비 가격대가 높아 세일이나 할인 기간을 기다리게 됨</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
     </row>
@@ -3424,27 +3256,11 @@
       <c r="J16" t="n">
         <v>152</v>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>훌륭한 포만감 — 하나만 꼭꼭 씹어 먹어도 한 끼 식사로 든든한 포만감이 오래 유지됨</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>실용적인 증정 보냉백 — 증정품으로 제공되는 보냉 가방이 유용하고 일상에서 쓰기 편함</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>오배송 및 문의 미흡 — 구성이 중복되거나 잘못 배송되었으나 고객센터와 연락이 잘 닿지 않음</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>포장 터짐 및 위생 불량 — 비닐 포장이 헐렁하게 마감되어 배송 도중 닭가슴살 소스가 터져서 묻어옴</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
     </row>
     <row r="17" ht="38" customHeight="1">
@@ -3487,21 +3303,9 @@
       <c r="J17" t="n">
         <v>217</v>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>깔끔하고 달콤한 맛 — 단백질 음료 고유의 비리고 텁텁한 뒷맛이 전혀 없고 초코우유처럼 달콤함</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>포만감 및 근성장 도움 — 운동 후 시원하게 마시기 좋고 배가 부르며 허기짐을 덜어주는 데 좋음</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>피부에 유용한 원료 — 피부 건강에 무해한 분리유청단백질 성분을 사용하여 만족도가 높음</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
@@ -3546,22 +3350,10 @@
       <c r="J18" t="n">
         <v>69</v>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>부드럽고 쫄깃한 식감 — 닭가슴살이 퍽퍽하지 않고 촉촉하며 매우 부드러워 다이어트에 제격임</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>먹기 편한 한입 형태 — 닭가슴살볼 타입은 한입 크기로 되어 있어 도시락이나 샐러드용으로 먹기 편리함</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>다소 아쉬운 배송 속도 — 주문 후 제품을 수령하기까지 걸리는 배송 기간이 다소 긴 편임</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
     </row>
@@ -3605,21 +3397,9 @@
       <c r="J19" t="n">
         <v>903</v>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>가벼워지는 배변 활동 — 꾸준히 섭취 시 변비 증상이 개선되고 아침에 몸이 한결 가벼워짐</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>풍성한 추가 증정 — 사은품으로 함께 동봉된 파로저당씬칩이 맛이 좋고 구매 구성이 푸짐함</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>정성스러운 정돈 포장 — 포장 겉면부터 정성이 듬뿍 느껴지게 정돈되어 수령 시 기쁨을 선사함</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
@@ -3664,33 +3444,17 @@
       <c r="J20" t="n">
         <v>21</v>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>우수한 숙취 해소 — 술자리 전후로 먹으면 다음 날 아침 두통이나 피로감이 크게 줄어듦</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>고급스러운 포장 백 — 리본 끈이 달린 전용 쇼핑백이 깔끔하게 포함되어 숙취해소 선물용으로 제격임</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>물 없는 간편한 섭취 — 스틱 하나만 뜯어서 바로 마시면 되므로 휴대와 복용이 대단히 쉬움</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>호불호 갈리는 쓴맛 — 한약재나 쌍화탕 같은 진한 맛이 다소 씁쓸하게 느껴져 맛에서 호불호가 갈림</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
     </row>
     <row r="21" ht="38" customHeight="1">
       <c r="B21" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3698,55 +3462,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>편안한 밤 필수템 식물성 멜라토닌 1mg 구미 젤리 멜라메이트 1박스 (50구미) 수험생/직장인 선물</t>
+          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CJ웰케어</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>18,900원</t>
+          <t>45,000원</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12065660</t>
+          <t>https://gift.kakao.com/product/7417420</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260126092430_c053db53f3d44b89900041b9c7968dc9.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260706153340_3e124da6e254462d9a7efad2521e3b9e.jpg</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>39</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>자연스러운 수면 유도 — 자기 전 복용하면 서서히 몸이 편안해지면서 도중에 깨지 않고 숙면을 취하게 됨</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>간식 같은 구미 제형 — 새콤달콤한 체리 맛과 쫄깃한 식감의 젤리 형태로 물 없이 맛있게 먹을 수 있음</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>넉넉한 수량 구성 — 한 박스에 넉넉한 50구미 구성으로 장기간 걱정 없이 든든하게 복용 가능함</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>취침 전 당 섭취 부담 — 물엿과 설탕이 첨가되어 밤늦게 이가 상하거나 당분을 섭취하는 점이 우려됨</t>
-        </is>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
     </row>
@@ -3896,12 +3644,12 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
           <t>홍삼/인삼</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -3938,14 +3686,14 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t>닥터블릿</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
           <t>뉴트리포유</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>닥터블릿</t>
-        </is>
-      </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
           <t>오쏘몰</t>
@@ -3953,12 +3701,12 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>오쏘몰</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
           <t>정관장</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -3995,14 +3743,14 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
+          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
           <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병</t>
-        </is>
-      </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
           <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 10입 - 추석 기프트 에디션 (공식수입)</t>
@@ -4010,12 +3758,12 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>'성별 맞춤 설계' 오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 - 시그니처 기프트 에디션 (공식수입)</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
           <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>'성별 맞춤 설계' 오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 - 시그니처 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -4071,107 +3819,51 @@
         <v>16226</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15539</v>
+        <v>15540</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3395</v>
+        <v>3396</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>6507</v>
       </c>
       <c r="G7" s="3" t="n">
+        <v>812</v>
+      </c>
+      <c r="H7" s="3" t="n">
         <v>8741</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>811</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>811</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1737</v>
+        <v>780</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>780</v>
+        <v>1740</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>948</v>
       </c>
     </row>
-    <row r="8" ht="90" customHeight="1">
+    <row r="8">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>뛰어난 피로 해소 — 피로 회복 및 에너지를 충전하는 데 큰 도움이 됨
-선물용으로 추천 — 포장과 구성이 고급스러워 감사한 마음을 전하는 선물용으로 매우 적합함
-편리한 액상 타입 — 액상과 알약 형태가 함께 들어있어 섭취가 편리하고 맛도 우수함</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>우수한 피로 회복 — 피곤할 때 섭취 시 아침이 개운해지고 활력을 되찾는 데 효과적임
-간편한 휴대와 섭취 — 물이 필요 없는 샷 제형으로 가방에 휴대하며 하나씩 꺼내 먹기 편리함
-거부감 없는 맛 — 망고맛 등 쥬스처럼 상큼하고 맛있어서 맛에 대한 거부감이 전혀 없음</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>빠른 피로 회복 — 힘들거나 피곤할 때 섭취하면 다음 날 몸이 가뿐해지는 것을 체감함
-고품격 패키지 디자인 — 포장 상태가 고급스러워 선물을 고를 때나 받을 때 만족도가 매우 높음</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>편리한 구미 제형 — 알약을 삼키기 힘들거나 수술 후 목넘김이 어려운 사람도 편하게 씹어 먹기 좋음
-우수한 맛과 식감 — 탱글하고 쫄깃한 식감에 맛이 좋아 간식처럼 매일 챙겨 먹기 적합함
-귀여운 패키지 — 감귤 모양의 손잡이가 달린 케이스와 귀여운 키캡 증정 구성으로 소장 가치가 높음</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>아침 활력 증진 — 피곤할 때 먹으면 기력 회복에 좋고 아침에 일어날 때 몸이 다르게 느껴짐
-알찬 에디션 구성 — 7입에 2입을 추가로 증정하여 가성비가 훌륭하고 단독 에디션 패키지가 깔끔함</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>휴대성과 편리함 — 가볍게 들고 다니며 물 없이 마시기 좋고 섭취 방법이 무척 간편함
-우수한 가성비 — 부담스러운 가격대의 타 브랜드 대비 합리적인 가격으로 구매하기 좋음
-신속한 배송 — 배송이 빠르고 안전하게 도착하여 기다림 없이 바로 섭취할 수 있음</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>선물에 최적화된 패키지 — 종이가방과 고급스러운 전용 박스 포장 덕분에 명절이나 감사의 선물로 제격임
-면역력 및 활력 개선 — 환절기 감기 예방과 지친 일상 속 빠른 면역력 관리에 매우 우수함</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>독특한 밀폐 용기 — 버튼을 눌러 섞어 마시는 신선한 방식으로 재미를 주며 변질 우려가 없음
-출산 및 육아 체력 관리 — 체력 소모가 극심한 출산 후 육아맘에게 활기를 북돋아 주는 센스 있는 선물임
-고급스러운 무게감 — 용기와 패키지에서 묵직한 고급스러움이 느껴지며 가격 부담도 적어 만족함</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>성별 맞춤 영양 설계 — 남성과 여성의 건강에 맞추어 선택이 가능하고 영양소 함량도 이뮨보다 풍부함
-쓴맛 없는 부드러움 — 비타민 특유의 쓰고 텁텁한 맛이 없어서 부담 없이 마시기에 용이함
-편리한 일상 휴대 — 가방에 가볍게 넣고 다닐 수 있는 콤팩트한 크기로 섭취가 간편함</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>믿을 수 있는 영국산 원료 — 고품질의 영국산 비타민C 원료를 사용하여 안전하고 신뢰를 줌
-우수한 컨디션 개선 — 복용 후 활력이 생기고 피부 건강과 아침 기상 시 가뿐함을 확실히 체감함</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -4179,27 +3871,14 @@
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>발송인 확인 불가 — 카카오톡 선물 수령 시 보낸 사람의 정보를 알기 어렵고 고객센터 문의도 미흡함</t>
-        </is>
-      </c>
+      <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>다소 아쉬운 부피 — 소포장 제품이라 선물로 건넸을 때 외관상 풍성해 보이지는 않음</t>
-        </is>
-      </c>
+      <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>자극적이고 신 맛 — 함량이 높아 신맛이 매우 자극적이고 맛이 없게 느껴질 수 있음
-복용이 불편한 제형 — 가루 형태라 입에 털어먹을 때 불편하므로 캡슐 형태로 개선되기를 희망함</t>
-        </is>
-      </c>
+      <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -4229,14 +3908,14 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
+          <t>52,900원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
           <t>19,900원</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>52,900원</t>
-        </is>
-      </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
           <t>43,900원</t>
@@ -4244,12 +3923,12 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>59,800원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
           <t>39,000원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>59,800원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -4442,7 +4121,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4178,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>CJ웰케어</t>
+          <t>익스트림</t>
         </is>
       </c>
     </row>
@@ -4556,7 +4235,7 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>편안한 밤 필수템 식물성 멜라토닌 1mg 구미 젤리 멜라메이트 1박스 (50구미) 수험생/직장인 선물</t>
+          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4283,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>60</v>
@@ -4631,123 +4310,42 @@
         <v>21</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" ht="90" customHeight="1">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="B20" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>맛있는 이색 효소 — 효소 특유의 불쾌한 맛없이 크림소다, 유자 등 새롭고 달달한 맛을 구현함
-효과적인 소화 도움 — 식사 후 가볍게 털어먹으면 속 더부룩함이 가라앉고 소화가 편해짐
-콜라보 굿즈 만족도 — 예쁜 리센느 포토카드와 엽서가 함께 포함되어 소장 가치를 더해줌</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>잡내 없는 촉촉함 — 닭가슴살 특유의 비린내가 전혀 나지 않고 부드러운 식감이 우수함
-다채로운 맛과 구성 — 다양한 종류와 양념으로 구성되어 질리지 않고 맛있게 식단을 관리할 수 있음</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>속이 편해지는 소화 — 밀가루나 과식을 한 뒤에 섭취하면 속 편안함과 뛰어난 소화력을 선사함
-구수한 고구마 맛 — 자극적이거나 텁텁하지 않고 구수한 고구마 맛이 나서 전 세대가 좋아함
-알찬 무료 증정품 — 곡물바, 차, 파로효소 등 맛있는 사은품이 넉넉하게 추가되어 혜택이 좋음</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>감동적인 전용 포장 — 오간자 에디션과 예쁜 전용 가방이 함께 구성되어 패키지를 열 때 기분이 무척 좋음
-비린 맛 없는 청량함 — 콜라겐 특유의 비린 맛 없이 상큼하고 깔끔하여 매일 먹기에 편안함</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>훌륭한 포만감 — 하나만 꼭꼭 씹어 먹어도 한 끼 식사로 든든한 포만감이 오래 유지됨
-실용적인 증정 보냉백 — 증정품으로 제공되는 보냉 가방이 유용하고 일상에서 쓰기 편함</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>깔끔하고 달콤한 맛 — 단백질 음료 고유의 비리고 텁텁한 뒷맛이 전혀 없고 초코우유처럼 달콤함
-포만감 및 근성장 도움 — 운동 후 시원하게 마시기 좋고 배가 부르며 허기짐을 덜어주는 데 좋음
-피부에 유용한 원료 — 피부 건강에 무해한 분리유청단백질 성분을 사용하여 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>부드럽고 쫄깃한 식감 — 닭가슴살이 퍽퍽하지 않고 촉촉하며 매우 부드러워 다이어트에 제격임
-먹기 편한 한입 형태 — 닭가슴살볼 타입은 한입 크기로 되어 있어 도시락이나 샐러드용으로 먹기 편리함</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>가벼워지는 배변 활동 — 꾸준히 섭취 시 변비 증상이 개선되고 아침에 몸이 한결 가벼워짐
-풍성한 추가 증정 — 사은품으로 함께 동봉된 파로저당씬칩이 맛이 좋고 구매 구성이 푸짐함
-정성스러운 정돈 포장 — 포장 겉면부터 정성이 듬뿍 느껴지게 정돈되어 수령 시 기쁨을 선사함</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>우수한 숙취 해소 — 술자리 전후로 먹으면 다음 날 아침 두통이나 피로감이 크게 줄어듦
-고급스러운 포장 백 — 리본 끈이 달린 전용 쇼핑백이 깔끔하게 포함되어 숙취해소 선물용으로 제격임
-물 없는 간편한 섭취 — 스틱 하나만 뜯어서 바로 마시면 되므로 휴대와 복용이 대단히 쉬움</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>자연스러운 수면 유도 — 자기 전 복용하면 서서히 몸이 편안해지면서 도중에 깨지 않고 숙면을 취하게 됨
-간식 같은 구미 제형 — 새콤달콤한 체리 맛과 쫄깃한 식감의 젤리 형태로 물 없이 맛있게 먹을 수 있음
-넉넉한 수량 구성 — 한 박스에 넉넉한 50구미 구성으로 장기간 걱정 없이 든든하게 복용 가능함</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="60" customHeight="1">
+      <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr"/>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
       <c r="B21" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>특정 라인업의 부재 — 가장 인기가 높은 그릴 형태의 파우치 제품이 구성에 빠져 있어 다소 아쉬움</t>
-        </is>
-      </c>
+      <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>다소 높은 가격대 — 일반 영양제 대비 가격대가 높아 세일이나 할인 기간을 기다리게 됨</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>오배송 및 문의 미흡 — 구성이 중복되거나 잘못 배송되었으나 고객센터와 연락이 잘 닿지 않음
-포장 터짐 및 위생 불량 — 비닐 포장이 헐렁하게 마감되어 배송 도중 닭가슴살 소스가 터져서 묻어옴</t>
-        </is>
-      </c>
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
       <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>다소 아쉬운 배송 속도 — 주문 후 제품을 수령하기까지 걸리는 배송 기간이 다소 긴 편임</t>
-        </is>
-      </c>
+      <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>호불호 갈리는 쓴맛 — 한약재나 쌍화탕 같은 진한 맛이 다소 씁쓸하게 느껴져 맛에서 호불호가 갈림</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>취침 전 당 섭취 부담 — 물엿과 설탕이 첨가되어 밤늦게 이가 상하거나 당분을 섭취하는 점이 우려됨</t>
-        </is>
-      </c>
+      <c r="K21" s="3" t="inlineStr"/>
+      <c r="L21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="B22" s="1" t="inlineStr">
@@ -4802,7 +4400,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>18,900원</t>
+          <t>45,000원</t>
         </is>
       </c>
     </row>
@@ -4992,7 +4590,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -5000,45 +4598,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>자연관 이뮨 멀티비타민 미네랄 4병</t>
+          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,500원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602124&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253277&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251216/mSQXyRQCV8ORV8edPm4n613602124_00_01mSQXyRQCV8ORV8edPm4n.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260422/eIhoZ9JSC5jbp33vSbZX987253277_00_01eIhoZ9JSC5jbp33vSbZX.jpg</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>1907</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>뛰어난 가성비 — 이뮨 멀티비타민을 파격적으로 저렴한 가격에 구입할 수 있어 만족스러움</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>빠른 피로 회복 — 피로감이 심하거나 기운이 없을 때 섭취하면 빠르게 신체 활력을 줌</t>
-        </is>
-      </c>
+        <v>829</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -5047,7 +4637,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5055,45 +4645,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>휴럼 하루한포 유기농 야채분말 15포 15일분</t>
+          <t>대웅제약 비타민D 4000IU 10정 10일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157056&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000281&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260706/z42ScLP7B6TWURzgDPY0919157056_00_01z42ScLP7B6TWURzgDPY0.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260504/H44oDYbaAQPekxvnTd9T600000281_00_01H44oDYbaAQPekxvnTd9T.png</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>405</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>부족한 야채 섭취 해결 — 평소 챙겨 먹기 힘든 채소 영양소를 한 포로 맛있고 쉽게 채울 수 있음</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>다양한 취식 활용 — 그냥 가루 형태로 입에 털어 먹거나 기호에 따라 꿀을 타서 섭취하기 좋음</t>
-        </is>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -5102,7 +4684,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5110,54 +4692,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대웅제약 쏘팔메토 옥타코사놀 30캡슐 30일분</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000139&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/Am2C7Da2wracg1TigkAF600000139_00_00Am2C7Da2wracg1TigkAF.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J4" t="n">
-        <v>2420</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>무난한 보조식품 — 대웅제약 브랜드 신뢰도를 지닌 건강식품으로 매일 간편히 챙기기 좋음</t>
-        </is>
-      </c>
+        <v>2779</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>효과 체감의 아쉬움 — 반년 이상 긴 시간 꾸준히 먹었으나 신체적으로 오는 직접적인 효과는 적음</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5165,45 +4739,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>오브맘 멀티비타민＆미네랄 하루구미 30일분</t>
+          <t>[의약외품] 동화 퀵앤써액 복숭아 12ml 5포</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602128&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618634&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250922/8husYxWOSsou1qKUi5IE613602128_00_018husYxWOSsou1qKUi5IE.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260424/G3OpB4vFrKk7H6gBBjO3601618634_00_00G3OpB4vFrKk7H6gBBjO3.jpg</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>1116</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>편리한 비타민 섭취 — 물 없이 젤리 형태로 씹어서 간단히 영양 관리를 할 수 있고 식감도 우수함</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>장기 구매 만족도 — 가성비가 아주 훌륭하여 1년 넘게 계속해서 재구매할 정도로 만족함</t>
-        </is>
-      </c>
+        <v>826</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -5212,7 +4778,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5220,12 +4786,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>오브맘 비타민C＆E 하루구미 30일분</t>
+          <t>[보령약국 X Pantio] [인교진 PICK] 다이어트 컷 올인원 15포 15일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>판티오</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5235,43 +4801,31 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602131&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=033991021&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250922/jrLxfLkWCczsCAsnqLoJ613602131_00_01jrLxfLkWCczsCAsnqLoJ.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260928/FbxeJLkidw2iKLnCp7Pe033991021_00_00FbxeJLkidw2iKLnCp7Pe.jpg</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>1002</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>비타민 타임의 즐거움 — 맛이 매우 뛰어난 편이라 챙겨 먹는 시간이 즐겁고 온 가족이 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>안심되는 넉넉한 기한 — 유통기한이 무척 넉넉하게 남아 있어 장기간 두고 안심하며 복용함</t>
-        </is>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>다소 약한 새콤함 — 기대했던 레몬맛 특유의 상큼하거나 새콤한 자극이 덜해 다소 평이함</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5279,50 +4833,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>홀베리 유기농 레몬즙 10포</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=965923434&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260305/6AQS4j3WbfucTbhmJ4ur965923434_00_006AQS4j3WbfucTbhmJ4ur.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>1645</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>부담 없는 상시 복용 — 그때그때 한 상자씩 가성비 넘치게 사다 먹기 가장 좋은 데일리 건강식임</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>정교한 개별 계량 — 번거로운 계량 작업이 필요 없도록 한 포씩 소분 포장되어 위생적임</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>다양한 음료 제조 — 집에서 간편하게 고품질의 탄산 레몬에이드를 만들어 마시기 탁월함</t>
-        </is>
-      </c>
+        <v>6630</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -5330,7 +4872,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5338,12 +4880,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>종근당건강 혈행건강엔 rTG오메가3 비타민 ADE 30캡슐 30일분</t>
+          <t>동국제약 이너케어＆유산균 30캡슐</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -5353,43 +4895,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591581111&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910677&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260424/ryqqbn8htR0Ir3fAZcjp591581111_00_01ryqqbn8htR0Ir3fAZcjp.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250829/mBCVgsNacUdX2MZDROO3610910677_00_00mBCVgsNacUdX2MZDROO3.png</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>867</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>한 알로 올인원 케어 — 오메가3 외에도 비타민 A, D, E를 알약 한 알로 끝낼 수 있어 비할 바 없이 편리함</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>간편한 한 달 용량 — 딱 30일 복용량이 소포장 정돈되어 보관이 편하고 상시 섭취하기 편리함</t>
-        </is>
-      </c>
+        <v>2876</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>삼키기 부담스러운 크기 — 캡슐의 외형이 일반적인 알약보다 다소 크게 느껴져 목넘김 시 주저함이 생김</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5397,12 +4927,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국제약 프라임도스 비타민B 맥스 30정 30일분</t>
+          <t>대웅제약 마그네슘 샷 25ml x 5병 5일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -5412,43 +4942,31 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911093&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000204&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260814/Q823T3m7aYDYd4gzOILy610911093_00_01Q823T3m7aYDYd4gzOILy.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20251121/aHjoRwP9ejVVuu8M0Td4600000204_00_01aHjoRwP9ejVVuu8M0Td4.png</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J9" t="n">
-        <v>76</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>높은 함량과 우수 성분 — 일반 시중 비타민B 라인업보다 비타민 성분 함량이 훨씬 고함량이라 든든함</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>가성비의 만족 — 매우 저렴한 가격에 높은 퀄리티의 제품을 공급하여 상시 복용에 가치가 있음</t>
-        </is>
-      </c>
+        <v>1443</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>체감 효능 지연 — 복용 초반 단계에서는 뚜렷한 건강 개선이나 활력 변화를 쉽게 느끼기 힘듦</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5456,12 +4974,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국제약 프라임도스 비타민C 2000 30포 30일분</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -5471,43 +4989,31 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911092&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260814/qU3FUPerTqzVYxrqf7Lx610911092_00_01qU3FUPerTqzVYxrqf7Lx.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>156</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>간편한 분할 소포장 — 스틱 포장으로 한 번에 한 포씩 뜯어서 물 없이 바로 섭취하기에 대단히 편함</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>놀라운 가격적 강점 — 소비자가 느끼는 가성비가 엄청나게 높아서 다이소 최고의 영양제로 손꼽힘</t>
-        </is>
-      </c>
+        <v>6581</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>강하고 자극적인 맛 — 비타민 본연의 고농축 함량 탓인지 맛이 매우 세거나 입안에서 쓰게 느껴짐</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5515,12 +5021,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>오브맘 기억력 그린라이트 30일분</t>
+          <t>LG생활건강 이너뷰 다이어트 가르시니아 10포</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -5530,36 +5036,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=913624077&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953535&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250519/l4wgtUT4J6F7QmnnIAOw913624077_00_00l4wgtUT4J6F7QmnnIAOw.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/nv6m1SoKa2Zw57OA3JHL994953535_00_00nv6m1SoKa2Zw57OA3JHL.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4.7</v>
       </c>
       <c r="J11" t="n">
-        <v>660</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>삼키기 편리한 알약 — 알약 입자 크기가 콤팩트하고 작아서 알약을 잘 못 삼키는 사람에게도 용이함</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>두뇌 및 인지 건강 개선 — 기억력 감퇴를 예방하거나 공부하는 수험생들의 인지 능력 보조제로 훌륭함</t>
-        </is>
-      </c>
+        <v>1064</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>즉각적인 체감 미흡 — 의약품이 아니기 때문에 단기 섭취만으로는 즉각적인 인지 향상 효과가 보이지 않음</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -5674,52 +5168,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
           <t>루테인/눈건강</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
     </row>
@@ -5731,52 +5225,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>동화약품</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>판티오</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>오브맘</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>오브맘</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>홀베리</t>
-        </is>
-      </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
     </row>
@@ -5788,52 +5282,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>자연관 이뮨 멀티비타민 미네랄 4병</t>
+          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>휴럼 하루한포 유기농 야채분말 15포 15일분</t>
+          <t>대웅제약 비타민D 4000IU 10정 10일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 쏘팔메토 옥타코사놀 30캡슐 30일분</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>오브맘 멀티비타민＆미네랄 하루구미 30일분</t>
+          <t>[의약외품] 동화 퀵앤써액 복숭아 12ml 5포</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>오브맘 비타민C＆E 하루구미 30일분</t>
+          <t>[보령약국 X Pantio] [인교진 PICK] 다이어트 컷 올인원 15포 15일분</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>홀베리 유기농 레몬즙 10포</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>종근당건강 혈행건강엔 rTG오메가3 비타민 ADE 30캡슐 30일분</t>
+          <t>동국제약 이너케어＆유산균 30캡슐</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국제약 프라임도스 비타민B 맥스 30정 30일분</t>
+          <t>대웅제약 마그네슘 샷 25ml x 5병 5일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국제약 프라임도스 비타민C 2000 30포 30일분</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>오브맘 기억력 그린라이트 30일분</t>
+          <t>LG생활건강 이너뷰 다이어트 가르시니아 10포</t>
         </is>
       </c>
     </row>
@@ -5847,10 +5341,10 @@
         <v>4.8</v>
       </c>
       <c r="D6" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>4.7</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>4.8</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>4.8</v>
@@ -5865,10 +5359,10 @@
         <v>4.8</v>
       </c>
       <c r="J6" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K6" s="3" t="n">
         <v>4.8</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>4.7</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>4.7</v>
@@ -5881,102 +5375,52 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1907</v>
+        <v>829</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>405</v>
+        <v>326</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2420</v>
+        <v>2779</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1116</v>
+        <v>826</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1002</v>
+        <v>252</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1645</v>
+        <v>6630</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>867</v>
+        <v>2876</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>76</v>
+        <v>1443</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>156</v>
+        <v>6581</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>뛰어난 가성비 — 이뮨 멀티비타민을 파격적으로 저렴한 가격에 구입할 수 있어 만족스러움
-빠른 피로 회복 — 피로감이 심하거나 기운이 없을 때 섭취하면 빠르게 신체 활력을 줌</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>부족한 야채 섭취 해결 — 평소 챙겨 먹기 힘든 채소 영양소를 한 포로 맛있고 쉽게 채울 수 있음
-다양한 취식 활용 — 그냥 가루 형태로 입에 털어 먹거나 기호에 따라 꿀을 타서 섭취하기 좋음</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>무난한 보조식품 — 대웅제약 브랜드 신뢰도를 지닌 건강식품으로 매일 간편히 챙기기 좋음</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>편리한 비타민 섭취 — 물 없이 젤리 형태로 씹어서 간단히 영양 관리를 할 수 있고 식감도 우수함
-장기 구매 만족도 — 가성비가 아주 훌륭하여 1년 넘게 계속해서 재구매할 정도로 만족함</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>비타민 타임의 즐거움 — 맛이 매우 뛰어난 편이라 챙겨 먹는 시간이 즐겁고 온 가족이 먹기 좋음
-안심되는 넉넉한 기한 — 유통기한이 무척 넉넉하게 남아 있어 장기간 두고 안심하며 복용함</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>부담 없는 상시 복용 — 그때그때 한 상자씩 가성비 넘치게 사다 먹기 가장 좋은 데일리 건강식임
-정교한 개별 계량 — 번거로운 계량 작업이 필요 없도록 한 포씩 소분 포장되어 위생적임
-다양한 음료 제조 — 집에서 간편하게 고품질의 탄산 레몬에이드를 만들어 마시기 탁월함</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>한 알로 올인원 케어 — 오메가3 외에도 비타민 A, D, E를 알약 한 알로 끝낼 수 있어 비할 바 없이 편리함
-간편한 한 달 용량 — 딱 30일 복용량이 소포장 정돈되어 보관이 편하고 상시 섭취하기 편리함</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>높은 함량과 우수 성분 — 일반 시중 비타민B 라인업보다 비타민 성분 함량이 훨씬 고함량이라 든든함
-가성비의 만족 — 매우 저렴한 가격에 높은 퀄리티의 제품을 공급하여 상시 복용에 가치가 있음</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>간편한 분할 소포장 — 스틱 포장으로 한 번에 한 포씩 뜯어서 물 없이 바로 섭취하기에 대단히 편함
-놀라운 가격적 강점 — 소비자가 느끼는 가성비가 엄청나게 높아서 다이소 최고의 영양제로 손꼽힘</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>삼키기 편리한 알약 — 알약 입자 크기가 콤팩트하고 작아서 알약을 잘 못 삼키는 사람에게도 용이함
-두뇌 및 인지 건강 개선 — 기억력 감퇴를 예방하거나 공부하는 수험생들의 인지 능력 보조제로 훌륭함</t>
-        </is>
-      </c>
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="1" t="inlineStr">
@@ -5986,38 +5430,14 @@
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>효과 체감의 아쉬움 — 반년 이상 긴 시간 꾸준히 먹었으나 신체적으로 오는 직접적인 효과는 적음</t>
-        </is>
-      </c>
+      <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>다소 약한 새콤함 — 기대했던 레몬맛 특유의 상큼하거나 새콤한 자극이 덜해 다소 평이함</t>
-        </is>
-      </c>
+      <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>삼키기 부담스러운 크기 — 캡슐의 외형이 일반적인 알약보다 다소 크게 느껴져 목넘김 시 주저함이 생김</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>체감 효능 지연 — 복용 초반 단계에서는 뚜렷한 건강 개선이나 활력 변화를 쉽게 느끼기 힘듦</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>강하고 자극적인 맛 — 비타민 본연의 고농축 함량 탓인지 맛이 매우 세거나 입안에서 쓰게 느껴짐</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>즉각적인 체감 미흡 — 의약품이 아니기 때문에 단기 섭취만으로는 즉각적인 인지 향상 효과가 보이지 않음</t>
-        </is>
-      </c>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -6027,32 +5447,32 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>1,500원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>1,000원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>2,000원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -6259,27 +5679,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[비건인증/총 4개월분] GNM 활성 엽산 800 비타민B 2박스</t>
+          <t>[올영단독] 칼로 스탑/컨트롤 PLUS 15포 2종</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>GNM자연의품격</t>
+          <t>칼로(Kalo)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24,900원</t>
+          <t>10,900원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=B000000209492&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000186228&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/B00000020949222ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018622875ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -6337,7 +5757,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -6345,27 +5765,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[피부건강] 글로우뮤즈 스킨 밸런스 파우더 레몬맛 14포 (14일분)</t>
+          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>26,800원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000246272&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000175634&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024627206ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017563488ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -6388,27 +5808,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>31,400원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -6423,7 +5843,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -6431,40 +5851,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[속광콜라겐] 글로우뮤즈 올데이 글로우 콜라겐 복숭아 14포 (14일분)</t>
+          <t>[1일 1정] 바이탈뷰티 메타그린 슬림업 30일</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>바이탈뷰티</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>22,900원</t>
+          <t>24,900원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000246271&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000248462&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024627107ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>163</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>건강을 위한 이너뷰티 — 피부 속 광채와 전신 건강을 한 번에 유지하기 위해 매일 간편하게 챙겨 먹기 좋음</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024846233ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -6482,31 +5894,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[1+1]알디콤 Plus 숙취해소제 21ml 4포입</t>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>알디콤</t>
+          <t>생활약속</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17,300원</t>
+          <t>16,200원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000227457&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000180121&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022745735ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012128ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>17202</v>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
@@ -6517,7 +5933,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -6525,27 +5941,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[품절대란] 닥터아돌 카테킨 아세로라 칼시페롤 C D 60정 (+시나모롤 틴케이스 키링)</t>
+          <t>온리추얼 비타민C 글로우업 트리플 7포+1포 (8일분)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>닥터아돌</t>
+          <t>온리추얼</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>26,900원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000218073&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000263899&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021807374ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026389913ko.png?l=ko</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -6560,7 +5976,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -6568,50 +5984,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[단독기획] 비비랩 저분자콜라겐S 30포 단품/더블기획 (1개월/2개월분)</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>비비랩</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>29,800원</t>
+          <t>27,400원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000208888&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020888832ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4.9</v>
       </c>
       <c r="J9" t="n">
-        <v>9466</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>물 없는 이너뷰티 습관 — 어려운 루틴 없이 물 없이도 입안에 가볍게 털어먹을 수 있어 장기 유지가 잘 됨</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>가을철 피부 탄력 관리 — 환절기 건조해지기 쉬운 피부 탄력을 내부에서부터 쫀쫀하게 채우는 데 도움을 줌</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>할인 기간 쟁임 템 — 올리브영 정기 세일 및 쿠폰 할인을 활용해 대량으로 쟁여두고 먹기에 합리적임</t>
-        </is>
-      </c>
+        <v>25664</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -6619,7 +6023,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -6627,50 +6031,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 12종 택 1</t>
+          <t>바이탈헬스 바이탈슬림 다이어트 올인원 데이 20포 (10일분)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>씨제이웰케어</t>
+          <t>바이탈헬스</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5,900원</t>
+          <t>23,890원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000154329&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024786106ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J10" t="n">
-        <v>19809</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>압도적인 저렴함 — 타사 유사 제품군 대비 매우 저렴한 단가로 부담 없이 장기 복용할 수 있음</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>안전하고 간편한 개별 포장 — 하나씩 소포장 설계되어 위생에 매우 좋고 일상이나 여행 가방에 간편 보관함</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>한 알로 기초 건강 보강 — 여러 번 번거롭게 나눠 먹을 필요 없이 복합 비타민과 필수 미네랄을 단번에 섭취함</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0015/A00000015432906ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -6678,7 +6066,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -6686,50 +6074,34 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>오니스트 트리플콜라겐 오렌지 14일 (+스크런치 증정)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>오니스트</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>31,400원</t>
+          <t>33,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000188804&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>8392</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>기쁨을 주는 사은 혜택 — 귀여운 카카오 키링이나 좋아하는 모델의 포토카드 등 소장하고 싶은 증정품을 제공함</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>여성을 위한 질 유산균 — 바쁜 아침 공복 상태에서 물과 함께 한 캡슐 섭취로 장과 질 건강을 동시에 관리함</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>장기 복용 더블 세트 — 단품이 아닌 알찬 더블 팩 기획 구성으로 두 달 동안 넉넉하게 영양소를 보강함</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018880437ko.png?l=ko</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -6855,42 +6227,42 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
           <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
     </row>
@@ -6902,7 +6274,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>GNM자연의품격</t>
+          <t>칼로(Kalo)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -6912,42 +6284,42 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>바이탈뷰티</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>생활약속</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>온리추얼</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>지노마스터</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>글로우뮤즈</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>알디콤</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>닥터아돌</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>비비랩</t>
-        </is>
-      </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>씨제이웰케어</t>
+          <t>바이탈헬스</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>오니스트</t>
         </is>
       </c>
     </row>
@@ -6959,7 +6331,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>[비건인증/총 4개월분] GNM 활성 엽산 800 비타민B 2박스</t>
+          <t>[올영단독] 칼로 스탑/컨트롤 PLUS 15포 2종</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -6969,42 +6341,42 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>[피부건강] 글로우뮤즈 스킨 밸런스 파우더 레몬맛 14포 (14일분)</t>
+          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>[1일 1정] 바이탈뷰티 메타그린 슬림업 30일</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>온리추얼 비타민C 글로우업 트리플 7포+1포 (8일분)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
           <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>[속광콜라겐] 글로우뮤즈 올데이 글로우 콜라겐 복숭아 14포 (14일분)</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>[1+1]알디콤 Plus 숙취해소제 21ml 4포입</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>[품절대란] 닥터아돌 카테킨 아세로라 칼시페롤 C D 60정 (+시나모롤 틴케이스 키링)</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>[단독기획] 비비랩 저분자콜라겐S 30포 단품/더블기획 (1개월/2개월분)</t>
-        </is>
-      </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 12종 택 1</t>
+          <t>바이탈헬스 바이탈슬림 다이어트 올인원 데이 20포 (10일분)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>오니스트 트리플콜라겐 오렌지 14일 (+스크런치 증정)</t>
         </is>
       </c>
     </row>
@@ -7018,20 +6390,16 @@
       <c r="D6" s="3" t="inlineStr"/>
       <c r="E6" s="3" t="inlineStr"/>
       <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="H6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="n">
+        <v>4.8</v>
+      </c>
       <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="K6" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>4.9</v>
-      </c>
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="1" t="inlineStr">
@@ -7043,22 +6411,18 @@
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="n">
-        <v>163</v>
-      </c>
-      <c r="H7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="n">
+        <v>17202</v>
+      </c>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="n">
-        <v>9466</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>19809</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>8392</v>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+        <v>25664</v>
+      </c>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -7068,34 +6432,12 @@
       <c r="D8" s="3" t="inlineStr"/>
       <c r="E8" s="3" t="inlineStr"/>
       <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>건강을 위한 이너뷰티 — 피부 속 광채와 전신 건강을 한 번에 유지하기 위해 매일 간편하게 챙겨 먹기 좋음</t>
-        </is>
-      </c>
+      <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>물 없는 이너뷰티 습관 — 어려운 루틴 없이 물 없이도 입안에 가볍게 털어먹을 수 있어 장기 유지가 잘 됨
-가을철 피부 탄력 관리 — 환절기 건조해지기 쉬운 피부 탄력을 내부에서부터 쫀쫀하게 채우는 데 도움을 줌
-할인 기간 쟁임 템 — 올리브영 정기 세일 및 쿠폰 할인을 활용해 대량으로 쟁여두고 먹기에 합리적임</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>압도적인 저렴함 — 타사 유사 제품군 대비 매우 저렴한 단가로 부담 없이 장기 복용할 수 있음
-안전하고 간편한 개별 포장 — 하나씩 소포장 설계되어 위생에 매우 좋고 일상이나 여행 가방에 간편 보관함
-한 알로 기초 건강 보강 — 여러 번 번거롭게 나눠 먹을 필요 없이 복합 비타민과 필수 미네랄을 단번에 섭취함</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>기쁨을 주는 사은 혜택 — 귀여운 카카오 키링이나 좋아하는 모델의 포토카드 등 소장하고 싶은 증정품을 제공함
-여성을 위한 질 유산균 — 바쁜 아침 공복 상태에서 물과 함께 한 캡슐 섭취로 장과 질 건강을 동시에 관리함
-장기 복용 더블 세트 — 단품이 아닌 알찬 더블 팩 기획 구성으로 두 달 동안 넉넉하게 영양소를 보강함</t>
-        </is>
-      </c>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="1" t="inlineStr">
@@ -7122,52 +6464,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>10,900원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>35,800원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>17,900원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>31,400원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
           <t>24,900원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>35,800원</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>26,800원</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>16,200원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>17,900원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>27,400원</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>22,900원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>17,300원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>26,900원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>29,800원</t>
-        </is>
-      </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>5,900원</t>
+          <t>23,890원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>31,400원</t>
+          <t>33,000원</t>
         </is>
       </c>
     </row>
@@ -7255,7 +6597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7293,117 +6635,117 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>35</v>
+        <v>32.5</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>22.5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
         <v>1</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -7413,32 +6755,32 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -7447,7 +6789,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -7457,12 +6799,56 @@
         <v>2.5</v>
       </c>
       <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
         <v>1</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>0</v>
       </c>
-      <c r="F9" t="n">
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>홍삼/인삼</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
         <v>0</v>
       </c>
     </row>
